--- a/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
+++ b/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
@@ -22,13 +22,13 @@
     <sheet name="Test Runs" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivery gate'!$A$4:$J$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Traceability'!$A$4:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Use Case Coverage'!$A$4:$J$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase 1A'!$A$4:$V$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivery gate'!$A$4:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Traceability'!$A$4:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Use Case Coverage'!$A$4:$Y$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase 1A'!$A$4:$V$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase 1B'!$A$4:$V$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Recipe coverage'!$A$4:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase 1C'!$A$4:$V$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase 1C'!$A$4:$V$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Regression'!$A$4:$V$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Non-functional'!$A$4:$V$20</definedName>
   </definedNames>
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,6 +161,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -682,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -697,180 +701,216 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>Derived from WeQuote-CRM-Phase-1-PRD.html — acceptance criteria (§B3), requirements (§B2) and the delivery gate (§A14).</t>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Derived from WeQuote-CRM-Phase-1-PRD.html — acceptance criteria (§B3), requirements (§B2) and the delivery gate (§A15).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr"/>
-      <c r="B3" s="21" t="inlineStr"/>
+      <c r="A3" s="17" t="inlineStr"/>
+      <c r="B3" s="23" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Summary · Delivery gate · Phase 1A / 1B / 1C · Recipe coverage · Regression</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Test Plan · Summary · Delivery gate · Traceability · Use Case Coverage · Phase 1A / 1B / 1C · Recipe coverage · Regression · Non-functional · Test Runs</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>What is in here</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Five separate populations: core functional cases, regression cases, non-functional cases, end-to-end journeys, and the recipe matrix. The Summary counts each one. Do not quote a single number for the whole plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>End-to-end journeys</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>On Use Case Coverage. Each one is a test you run start to finish and record in Status. The three columns on the right read the granular cases behind it — those passing is a readiness hint, not proof the journey ran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Concurrency, event order, partial failure, performance, permissions, accessibility, browsers, audit, recovery. Each names the release it gates in Applies from, and the Summary counts it into that release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Fill in</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Status onwards. Everything left of Status describes the test and should not be edited.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Status values</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Not run · Pass · Fail · Blocked · N/A</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>What blocks a release</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Fail, Blocked and Not run block. Pass and N/A do not.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Using N/A</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Only for a test that cannot apply to this release. It must carry a reason in Notes and a name in 'Waiver approved by'. The Summary counts unapproved N/A separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Only for a test that cannot apply to this release. It must carry a reason in Notes AND a name in 'Waiver approved by'. The Summary counts every N/A missing either one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Applies from</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>On Regression, the earliest release a rule can be tested in. A Phase 1A gate only counts rules that apply from Phase 1A.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Manual, Automated or Both. The PRD requires the resolver, tenancy and duplicate tests to be automated — record the CI link under Evidence.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>P1 must pass before the release ships. P2 needs a named owner to accept any exception. P3 is optional.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Date format</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr"/>
+      <c r="B16" s="23" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Example row</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Status: Fail  ·  Actual result: Deal stayed in Qualified  ·  Build: 1A-rc3  ·  Environment: Staging  ·  Browser: Chrome 141 / macOS  ·  Test data: D-0348  ·  Evidence: jira/WQ-1183  ·  Defect ID: WQ-1183  ·  Tester: KW  ·  Date: 2026-09-04</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr"/>
+      <c r="B18" s="23" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>1. Tests marked 'cond. D1' apply only if backward Deal movement is approved.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr"/>
-      <c r="B17" s="21" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr"/>
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>2. D5 tests have no fixed expected result until the over-quota and sales-order ruling is recorded.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr"/>
-      <c r="B18" s="21" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr"/>
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>3. D7 decides whose approval threshold applies; the approval boundary tests inherit that answer.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr"/>
-      <c r="B19" s="21" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr"/>
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>4. Phase 1B and 1C assume the preceding release passed its own P1 tests.</t>
         </is>
@@ -887,15 +927,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
@@ -2085,7 +2125,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Simulator</t>
+          <t>Editing</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2100,22 +2140,22 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>A draft ready to test.</t>
+          <t>A published Automation that is live and firing.</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Run a test.</t>
+          <t>Change one step, press Save Draft, then fire the Automation's trigger.</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Timeline opens as the default tab. No live CRM record is created, changed or deleted, and the result says so explicitly.</t>
+          <t>Only the draft is saved. The live version is untouched and still runs on the trigger, and the run history names the published version, not the draft.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>FR-12 / AC-BLD-09</t>
+          <t>FR-12, FR-13 / AC-BLD-11</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -2168,22 +2208,22 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>A test running.</t>
+          <t>A draft ready to test.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Use Play, Step, Reset and Speed.</t>
+          <t>Run a test.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Play runs the flow, Step advances one step, Reset returns to the start and Speed changes the playback rate. All four respond.</t>
+          <t>Timeline opens as the default tab. No live CRM record is created, changed or deleted, and the result says so explicitly.</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>AC-BLD-09</t>
+          <t>FR-12 / AC-BLD-09</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -2221,7 +2261,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Publish</t>
+          <t>Simulator</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -2236,22 +2276,22 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>A valid draft, never tested.</t>
+          <t>A test running.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Publish it.</t>
+          <t>Use Play, Step, Reset and Speed.</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Publishing succeeds. A missing or outdated test does not block it, and the published version is recorded.</t>
+          <t>Play runs the flow, Step advances one step, Reset returns to the start and Speed changes the playback rate. All four respond.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>FR-13 / AC-BLD-10</t>
+          <t>AC-BLD-09</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -2289,7 +2329,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Publish</t>
+          <t>Simulator</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2304,22 +2344,22 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>A draft ready to publish.</t>
+          <t>A draft with unsaved changes.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Open the publish confirmation.</t>
+          <t>Press Test automation, then edit the draft again while the result is open.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>It shows Before &amp; After, the company scope and the test status.</t>
+          <t>A Test Draft snapshot is saved before the run, and the run executes against that snapshot. The later edit does not change what was tested; the result stays tied to the snapshot it ran on.</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>FR-13 / AC-BLD-09</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2357,7 +2397,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Publish</t>
+          <t>Simulator</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -2372,22 +2412,22 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>A draft ready to publish.</t>
+          <t>A finished test run on a draft that creates a note, a meeting, a next action and a file request.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Publish it.</t>
+          <t>Open Before &amp; After.</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>The live version is replaced in one step and the previous version recorded.</t>
+          <t>It lists the actual CRM records and fields the publish would produce — the note, the meeting, the next action and the file request, each named — not two copies of the flow diagram.</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>FR-14</t>
+          <t>FR-13 / AC-BLD-09</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -2440,22 +2480,22 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>An action missing required configuration.</t>
+          <t>A valid draft, never tested.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Try to publish.</t>
+          <t>Publish it.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The offending step is highlighted, the reason names the missing configuration, the draft stays saved, and the live version keeps running unchanged.</t>
+          <t>Publishing succeeds. A missing or outdated test does not block it, and the published version is recorded.</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>FR-13 / AC-BLD-10</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2508,17 +2548,17 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>A deleted target stage referenced.</t>
+          <t>A draft ready to publish.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Try to publish.</t>
+          <t>Open the publish confirmation.</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The step referencing the deleted stage is highlighted, the draft stays saved, and the live version keeps running unchanged.</t>
+          <t>It shows Before &amp; After, the company scope and the test status.</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -2576,22 +2616,22 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>A file-received trigger pointing at a removed request.</t>
+          <t>A draft ready to publish.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Try to publish.</t>
+          <t>Publish it.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The trigger is highlighted with a reason naming the missing file request, the draft stays saved, and the live version keeps running unchanged.</t>
+          <t>The live version is replaced in one step and the previous version recorded.</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>FR-14</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2644,7 +2684,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>A branch that loops back on itself.</t>
+          <t>An action missing required configuration.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -2654,7 +2694,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The looping branch is highlighted, the reason explains the cycle, the draft stays saved, and the live version keeps running unchanged.</t>
+          <t>Publishing is blocked. The offending step is highlighted, the reason names the missing configuration, the draft stays saved, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -2712,7 +2752,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>A protected milestone used as a move target.</t>
+          <t>A deleted target stage referenced.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2722,7 +2762,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The move step is highlighted with a reason stating that protected milestones cannot be a move target, and the live version keeps running unchanged.</t>
+          <t>Publishing is blocked. The step referencing the deleted stage is highlighted, the draft stays saved, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -2780,7 +2820,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>A wait that cannot end.</t>
+          <t>A file-received trigger pointing at a removed request.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -2790,7 +2830,7 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>Publishing is blocked. The wait step is highlighted with a reason stating it has no safe ending, and the live version keeps running unchanged.</t>
+          <t>Publishing is blocked. The trigger is highlighted with a reason naming the missing file request, the draft stays saved, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2833,7 +2873,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Publish</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2848,22 +2888,22 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>A published Automation.</t>
+          <t>A branch that loops back on itself.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Toggle it Active then Inactive.</t>
+          <t>Try to publish.</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>The change takes effect immediately: an inactive Automation stops running, and both Map and List show the new state.</t>
+          <t>Publishing is blocked. The looping branch is highlighted, the reason explains the cycle, the draft stays saved, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>FR-15 / AC-BLD-12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2901,7 +2941,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Publish</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -2916,22 +2956,22 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>A pipeline with several Automations.</t>
+          <t>A protected milestone used as a move target.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Pause then resume at pipeline level.</t>
+          <t>Try to publish.</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>All Automations in the pipeline follow. The counts on Map and List stay in step.</t>
+          <t>Publishing is blocked. The move step is highlighted with a reason stating that protected milestones cannot be a move target, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -2969,12 +3009,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Publish</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2984,17 +3024,17 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Pipeline paused with impact comparison shown.</t>
+          <t>A wait that cannot end.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Compare it with a single-Automation test.</t>
+          <t>Try to publish.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>The two are visibly different features and are not confused in the interface.</t>
+          <t>Publishing is blocked. The wait step is highlighted with a reason stating it has no safe ending, and the live version keeps running unchanged.</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -3037,7 +3077,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>State</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -3052,22 +3092,22 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>An Automation published twice.</t>
+          <t>A published Automation.</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Open change history.</t>
+          <t>Toggle it Active then Inactive.</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Each entry records the version, the company scope, the user and the timestamp.</t>
+          <t>The change takes effect immediately: an inactive Automation stops running, and both Map and List show the new state.</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>FR-10</t>
+          <t>FR-15 / AC-BLD-12</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
@@ -3105,7 +3145,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>File request</t>
+          <t>State</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3120,22 +3160,22 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Building a flow with a requested-file-received trigger.</t>
+          <t>A pipeline with several Automations.</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Save without selecting a named request.</t>
+          <t>Pause then resume at pipeline level.</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Saving is refused. The trigger is highlighted with a reason that a real named file request must be selected first, and no partial flow is stored.</t>
+          <t>All Automations in the pipeline follow. The counts on Map and List stay in step.</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>FR-20 / AC-RUN-01</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -3173,12 +3213,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>File request</t>
+          <t>State</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -3188,22 +3228,22 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>A Deal with an open file request.</t>
+          <t>Pipeline paused with impact comparison shown.</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Upload the matching file.</t>
+          <t>Compare it with a single-Automation test.</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>The requirement resolves automatically across focus, history and card status.</t>
+          <t>The two are visibly different features and are not confused in the interface.</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>FR-20</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -3241,7 +3281,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Required work</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3256,22 +3296,22 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>A Deal with three outstanding requirements.</t>
+          <t>An Automation published twice.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Attempt a stage move.</t>
+          <t>Open change history.</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>All three listed, Continue disabled, each resolvable inline, original action resumes when empty.</t>
+          <t>Each entry records the version, the company scope, the user and the timestamp.</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>FR-19 / AC-RUN-02</t>
+          <t>FR-10</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -3309,7 +3349,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Required work</t>
+          <t>File request</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -3324,22 +3364,22 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Ten or more outstanding requirements.</t>
+          <t>Building a flow with a requested-file-received trigger.</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Attempt the blocked action.</t>
+          <t>Save without selecting a named request.</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Every outstanding item is listed with a scrollable dialog. Nothing is truncated, and the count in the heading matches the number of rows.</t>
+          <t>Saving is refused. The trigger is highlighted with a reason that a real named file request must be selected first, and no partial flow is stored.</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>FR-20 / AC-RUN-01</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Required work</t>
+          <t>File request</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3392,22 +3432,22 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>A blocked quote-lifecycle action.</t>
+          <t>A Deal with an open file request.</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Clear the list.</t>
+          <t>Upload the matching file.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>The exact original operation resumes, not a generic fallback.</t>
+          <t>The requirement resolves automatically across focus, history and card status.</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>FR-19</t>
+          <t>FR-20</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -3445,12 +3485,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Handoff</t>
+          <t>Required work</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3460,22 +3500,22 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Phase 1C shipped.</t>
+          <t>A Deal with three outstanding requirements.</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>Open a recipe as an editable copy.</t>
+          <t>Attempt a stage move.</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>The live recipe keeps running; the copy is independent and the move is stated as one-way.</t>
+          <t>All three listed, Continue disabled, each resolvable inline, original action resumes when empty.</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-19 / AC-RUN-02</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
@@ -3495,9 +3535,213 @@
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="9" t="inlineStr"/>
     </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>1C-37</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Required work</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Ten or more outstanding requirements.</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Attempt the blocked action.</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Every outstanding item is listed with a scrollable dialog. Nothing is truncated, and the count in the heading matches the number of rows.</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="4" t="inlineStr"/>
+      <c r="S41" s="4" t="inlineStr"/>
+      <c r="T41" s="4" t="inlineStr"/>
+      <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>1C-38</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Required work</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>A blocked quote-lifecycle action.</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Clear the list.</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>The exact original operation resumes, not a generic fallback.</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>FR-19</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr"/>
+      <c r="Q42" s="9" t="inlineStr"/>
+      <c r="R42" s="7" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr"/>
+      <c r="T42" s="7" t="inlineStr"/>
+      <c r="U42" s="8" t="inlineStr"/>
+      <c r="V42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>1C-39</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Handoff</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Phase 1C shipped.</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Open a recipe as an editable copy.</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>The live recipe keeps running; the copy is independent and the move is stated as one-way.</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="4" t="inlineStr"/>
+      <c r="S43" s="4" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:V40"/>
-  <conditionalFormatting sqref="K5:K40">
+  <autoFilter ref="A4:V43"/>
+  <conditionalFormatting sqref="K5:K43">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -3515,13 +3759,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="K5:K40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K5:K43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E5:E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Manual,Automated,Both"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3541,9 +3785,9 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
@@ -4149,9 +4393,9 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
@@ -4180,7 +4424,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Concurrency, event ordering, partial failure, performance, permissions, accessibility, browsers, audit and recovery.</t>
+          <t>Concurrency, event ordering, partial failure, performance, permissions, accessibility, browsers, audit and recovery. Applies from names the release each case gates — the Summary counts it there.</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4560,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1C</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4457,7 +4701,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Event order</t>
+          <t>Events arrive in a different order</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -4520,12 +4764,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Event order</t>
+          <t>Events arrive in a different order</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -4588,12 +4832,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Event order</t>
+          <t>Events arrive in a different order</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4656,12 +4900,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Partial failure</t>
+          <t>One action fails during a run</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -4724,12 +4968,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Partial failure</t>
+          <t>One action fails during a run</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5064,7 +5308,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1C</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -5132,7 +5376,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1C</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5336,7 +5580,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Phase 1A</t>
+          <t>Phase 1C</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -5555,77 +5799,77 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>1A-rc3</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Staging</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>Chrome 141 / macOS</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>Full Phase 1A + applicable Regression</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t>KW</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="J5" s="30" t="n">
+      <c r="J5" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="K5" s="30" t="n">
+      <c r="K5" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="30" t="n">
+      <c r="L5" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="30" t="n">
+      <c r="M5" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="30" t="n">
+      <c r="N5" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="30" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t>No-go</t>
         </is>
       </c>
-      <c r="P5" s="29" t="inlineStr">
+      <c r="P5" s="31" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>Two S2 defects open — WQ-1183, WQ-1190</t>
         </is>
@@ -6067,15 +6311,15 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
+      <c r="B4" s="29" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="28" t="n"/>
+      <c r="A5" s="30" t="n"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>• Prove the Deal stage is always derived from quotes and can never be typed in.</t>
@@ -6083,7 +6327,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="28" t="n"/>
+      <c r="A6" s="30" t="n"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
           <t>• Prove one customer account can never read or change another's records.</t>
@@ -6091,7 +6335,7 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="28" t="n"/>
+      <c r="A7" s="30" t="n"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
           <t>• Prove an Automation cannot approve, send, accept, or decide Won or Lost.</t>
@@ -6099,7 +6343,7 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="28" t="n"/>
+      <c r="A8" s="30" t="n"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
           <t>• Prove money figures — signed value, change orders, margin — agree with the quotes behind them.</t>
@@ -6107,7 +6351,7 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="28" t="n"/>
+      <c r="A9" s="30" t="n"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
           <t>• Prove each release can ship on its own without waiting for the next.</t>
@@ -6115,15 +6359,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>In scope</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n"/>
+      <c r="B11" s="29" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="n"/>
+      <c r="A12" s="30" t="n"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
           <t>• Lead, Deal, Customer, Company and Activity records.</t>
@@ -6131,7 +6375,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="28" t="n"/>
+      <c r="A13" s="30" t="n"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
           <t>• Quote-to-stage logic, alternative groups and change orders.</t>
@@ -6139,7 +6383,7 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="28" t="n"/>
+      <c r="A14" s="30" t="n"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t>• Deal value and the four margin figures.</t>
@@ -6147,7 +6391,7 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="28" t="n"/>
+      <c r="A15" s="30" t="n"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
           <t>• Managed recipes, their settings, scheduling and results.</t>
@@ -6155,7 +6399,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="n"/>
+      <c r="A16" s="30" t="n"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
           <t>• The advanced builder: catalogue, editing, testing, publishing, required work.</t>
@@ -6163,7 +6407,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="28" t="n"/>
+      <c r="A17" s="30" t="n"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
           <t>• Company-level visibility and account isolation.</t>
@@ -6171,15 +6415,15 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Out of scope</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n"/>
+      <c r="B19" s="29" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="n"/>
+      <c r="A20" s="30" t="n"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
           <t>• Forecast dashboards and weighted probability — Phase 2.</t>
@@ -6187,7 +6431,7 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="28" t="n"/>
+      <c r="A21" s="30" t="n"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
           <t>• Customer-created custom stages — Phase 2.</t>
@@ -6195,7 +6439,7 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="n"/>
+      <c r="A22" s="30" t="n"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>• Fully custom pipelines — Phase 3.</t>
@@ -6203,7 +6447,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="n"/>
+      <c r="A23" s="30" t="n"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
           <t>• Public web-to-lead forms — deferred.</t>
@@ -6211,7 +6455,7 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="n"/>
+      <c r="A24" s="30" t="n"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
           <t>• Zoho, QuickBooks and Xero behaviour beyond the coexistence rule in §C3.</t>
@@ -6219,15 +6463,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>Test levels</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n"/>
+      <c r="B26" s="29" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="n"/>
+      <c r="A27" s="30" t="n"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
           <t>• Component: stage logic, quote-inclusion test, value arithmetic — automated.</t>
@@ -6235,7 +6479,7 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="28" t="n"/>
+      <c r="A28" s="30" t="n"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
           <t>• Integration: quote event to Deal update to Automation run — automated.</t>
@@ -6243,7 +6487,7 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="n"/>
+      <c r="A29" s="30" t="n"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
           <t>• System: the end-to-end journeys on the Use Case Coverage sheet — manual.</t>
@@ -6251,7 +6495,7 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="28" t="n"/>
+      <c r="A30" s="30" t="n"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
           <t>• UAT: the same journeys run by Sales and an Admin on staging.</t>
@@ -6259,7 +6503,7 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="n"/>
+      <c r="A31" s="30" t="n"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
           <t>• Regression: the six locked rules, re-run in full before every release.</t>
@@ -6267,15 +6511,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
+      <c r="B33" s="29" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="n"/>
+      <c r="A34" s="30" t="n"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
           <t>• Automate anything the PRD names as automated: the precedence ladder, the quote-inclusion clauses, both revision flags, idempotency and account isolation.</t>
@@ -6283,7 +6527,7 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="n"/>
+      <c r="A35" s="30" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
           <t>• Everything else is manual, with evidence attached.</t>
@@ -6291,7 +6535,7 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="n"/>
+      <c r="A36" s="30" t="n"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
           <t>• Each test records its Method so automated coverage can be proven, not asserted.</t>
@@ -6299,15 +6543,15 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B38" s="27" t="n"/>
+      <c r="B38" s="29" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="28" t="n"/>
+      <c r="A39" s="30" t="n"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
           <t>• Staging, refreshed from a masked production copy before each release cycle.</t>
@@ -6315,7 +6559,7 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="28" t="n"/>
+      <c r="A40" s="30" t="n"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
           <t>• Build or commit recorded against every executed test.</t>
@@ -6323,7 +6567,7 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="n"/>
+      <c r="A41" s="30" t="n"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
           <t>• Timed recipes need the work queue running; note in Actual result if it was not.</t>
@@ -6331,15 +6575,15 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Test accounts</t>
         </is>
       </c>
-      <c r="B43" s="27" t="n"/>
+      <c r="B43" s="29" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="28" t="n"/>
+      <c r="A44" s="30" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
           <t>• Audio Vision Group with at least three companies, for company-scope tests.</t>
@@ -6347,7 +6591,7 @@
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="n"/>
+      <c r="A45" s="30" t="n"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
           <t>• A second unrelated account, for isolation tests.</t>
@@ -6355,7 +6599,7 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="28" t="n"/>
+      <c r="A46" s="30" t="n"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
           <t>• One Sales user limited to one company, one manager across all, one user with no CRM access.</t>
@@ -6363,7 +6607,7 @@
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="n"/>
+      <c r="A47" s="30" t="n"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
           <t>• An approver distinct from the quote owner, for the high-value approval tests.</t>
@@ -6371,15 +6615,15 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>Test data</t>
         </is>
       </c>
-      <c r="B49" s="27" t="n"/>
+      <c r="B49" s="29" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="28" t="n"/>
+      <c r="A50" s="30" t="n"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
           <t>• A Deal with three quotes in one alternative group.</t>
@@ -6387,7 +6631,7 @@
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="n"/>
+      <c r="A51" s="30" t="n"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
           <t>• A Deal with two independent quotes.</t>
@@ -6395,7 +6639,7 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="28" t="n"/>
+      <c r="A52" s="30" t="n"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
           <t>• A quote family whose latest revision is not the active one.</t>
@@ -6403,7 +6647,7 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="n"/>
+      <c r="A53" s="30" t="n"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
           <t>• One sample, one template and one archived quote.</t>
@@ -6411,7 +6655,7 @@
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="28" t="n"/>
+      <c r="A54" s="30" t="n"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
           <t>• An accepted quote with a signed change order.</t>
@@ -6419,7 +6663,7 @@
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="n"/>
+      <c r="A55" s="30" t="n"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
           <t>• At least one non-Sales pipeline with its own Deals.</t>
@@ -6427,15 +6671,15 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>Entry criteria</t>
         </is>
       </c>
-      <c r="B57" s="27" t="n"/>
+      <c r="B57" s="29" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="28" t="n"/>
+      <c r="A58" s="30" t="n"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
           <t>• The build is deployed to staging and smoke-passes.</t>
@@ -6443,7 +6687,7 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="28" t="n"/>
+      <c r="A59" s="30" t="n"/>
       <c r="B59" s="6" t="inlineStr">
         <is>
           <t>• The release's blocking Delivery gate items for Decisions and Data are Done.</t>
@@ -6451,7 +6695,7 @@
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="28" t="n"/>
+      <c r="A60" s="30" t="n"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
           <t>• Test data above is present.</t>
@@ -6459,7 +6703,7 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="n"/>
+      <c r="A61" s="30" t="n"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
           <t>• Known defects from the previous cycle are triaged.</t>
@@ -6467,15 +6711,15 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>Exit criteria</t>
         </is>
       </c>
-      <c r="B63" s="27" t="n"/>
+      <c r="B63" s="29" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="28" t="n"/>
+      <c r="A64" s="30" t="n"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
           <t>• Every P1 test for that release is Pass, or N/A with a reason and an approver.</t>
@@ -6483,7 +6727,7 @@
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="n"/>
+      <c r="A65" s="30" t="n"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
           <t>• No open defect of severity 1 or 2.</t>
@@ -6491,7 +6735,7 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="28" t="n"/>
+      <c r="A66" s="30" t="n"/>
       <c r="B66" s="6" t="inlineStr">
         <is>
           <t>• Every Blocking gate item for that release is Done.</t>
@@ -6499,7 +6743,7 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="n"/>
+      <c r="A67" s="30" t="n"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
           <t>• Automated tests named in the PRD are running in CI with a link recorded.</t>
@@ -6507,15 +6751,15 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="B69" s="27" t="n"/>
+      <c r="B69" s="29" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="28" t="n"/>
+      <c r="A70" s="30" t="n"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
           <t>• QA runs the cases and records results.</t>
@@ -6523,7 +6767,7 @@
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="n"/>
+      <c r="A71" s="30" t="n"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
           <t>• Engineering fixes defects and provides the CI links.</t>
@@ -6531,7 +6775,7 @@
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="28" t="n"/>
+      <c r="A72" s="30" t="n"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
           <t>• Product decides on N/A waivers and answers the open decisions.</t>
@@ -6539,7 +6783,7 @@
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="n"/>
+      <c r="A73" s="30" t="n"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
           <t>• Design confirms the interface behaviour cases.</t>
@@ -6547,7 +6791,7 @@
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="28" t="n"/>
+      <c r="A74" s="30" t="n"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
           <t>• CTO signs the release gate.</t>
@@ -6555,15 +6799,15 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Defect severity</t>
         </is>
       </c>
-      <c r="B76" s="27" t="n"/>
+      <c r="B76" s="29" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="n"/>
+      <c r="A77" s="30" t="n"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
           <t>• S1 — data loss, cross-account leakage, or a wrong Deal stage or value. Blocks the release.</t>
@@ -6571,7 +6815,7 @@
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="28" t="n"/>
+      <c r="A78" s="30" t="n"/>
       <c r="B78" s="6" t="inlineStr">
         <is>
           <t>• S2 — a documented rule not enforced, or a protected action reachable. Blocks the release.</t>
@@ -6579,7 +6823,7 @@
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="28" t="n"/>
+      <c r="A79" s="30" t="n"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
           <t>• S3 — wrong or missing feedback, recoverable. Fix or waive with an owner.</t>
@@ -6587,7 +6831,7 @@
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="28" t="n"/>
+      <c r="A80" s="30" t="n"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
           <t>• S4 — cosmetic. Backlog.</t>
@@ -6595,15 +6839,15 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>Retest and regression</t>
         </is>
       </c>
-      <c r="B82" s="27" t="n"/>
+      <c r="B82" s="29" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="28" t="n"/>
+      <c r="A83" s="30" t="n"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
           <t>• A fixed defect is retested on the build that contains the fix.</t>
@@ -6611,7 +6855,7 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="28" t="n"/>
+      <c r="A84" s="30" t="n"/>
       <c r="B84" s="6" t="inlineStr">
         <is>
           <t>• Any change to stage logic, value arithmetic or the block catalogue re-runs the whole Regression sheet.</t>
@@ -6619,7 +6863,7 @@
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="28" t="n"/>
+      <c r="A85" s="30" t="n"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
           <t>• A hotfix re-runs Regression plus the affected area.</t>
@@ -6627,15 +6871,15 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="inlineStr">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="B87" s="27" t="n"/>
+      <c r="B87" s="29" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="28" t="n"/>
+      <c r="A88" s="30" t="n"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
           <t>• The activity timeline is barely used today; adoption is unproven — see §A13 D3.</t>
@@ -6643,7 +6887,7 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="28" t="n"/>
+      <c r="A89" s="30" t="n"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
           <t>• Zoho-connected accounts must stay switched off until D2 is answered.</t>
@@ -6651,7 +6895,7 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="28" t="n"/>
+      <c r="A90" s="30" t="n"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
           <t>• Timed recipes depend on a work queue that does not exist yet.</t>
@@ -6659,7 +6903,7 @@
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="28" t="n"/>
+      <c r="A91" s="30" t="n"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
           <t>• Backward Deal movement is conditional on D1; those tests stay N/A until it is answered.</t>
@@ -6667,15 +6911,15 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>Release verification</t>
         </is>
       </c>
-      <c r="B93" s="27" t="n"/>
+      <c r="B93" s="29" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="28" t="n"/>
+      <c r="A94" s="30" t="n"/>
       <c r="B94" s="6" t="inlineStr">
         <is>
           <t>• After deploy, re-run the Regression sheet on production data for one pilot account.</t>
@@ -6683,7 +6927,7 @@
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="n"/>
+      <c r="A95" s="30" t="n"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
           <t>• Confirm the pipeline board, one Deal's value, and one recipe run.</t>
@@ -6691,7 +6935,7 @@
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="28" t="n"/>
+      <c r="A96" s="30" t="n"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
           <t>• Rollback plan: disable the CRM navigation entry; no data migration is reversed automatically.</t>
@@ -6709,10 +6953,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -6791,31 +7035,31 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA('Phase 1A'!$A$5:$A$58)</f>
+        <f>COUNTA('Phase 1A'!$A$5:$A$75)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$58,"Pass")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$58,"Fail")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$58,"Blocked")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$58,"N/A")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"N/A")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$58,"Not run")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Not run")</f>
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>COUNTIFS('Phase 1A'!$E$5:$E$58,"P1")-COUNTIFS('Phase 1A'!$E$5:$E$58,"P1",'Phase 1A'!$K$5:$K$58,"Pass")-COUNTIFS('Phase 1A'!$E$5:$E$58,"P1",'Phase 1A'!$K$5:$K$58,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")</f>
+        <f>COUNTIFS('Phase 1A'!$E$5:$E$75,"P1")-COUNTIFS('Phase 1A'!$E$5:$E$75,"P1",'Phase 1A'!$K$5:$K$75,"Pass")-COUNTIFS('Phase 1A'!$E$5:$E$75,"P1",'Phase 1A'!$K$5:$K$75,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")+COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
         <v/>
       </c>
       <c r="I5" s="11">
@@ -6854,7 +7098,7 @@
         <v/>
       </c>
       <c r="H6" s="5">
-        <f>COUNTIFS('Phase 1B'!$E$5:$E$29,"P1")-COUNTIFS('Phase 1B'!$E$5:$E$29,"P1",'Phase 1B'!$K$5:$K$29,"Pass")-COUNTIFS('Phase 1B'!$E$5:$E$29,"P1",'Phase 1B'!$K$5:$K$29,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")</f>
+        <f>COUNTIFS('Phase 1B'!$E$5:$E$29,"P1")-COUNTIFS('Phase 1B'!$E$5:$E$29,"P1",'Phase 1B'!$K$5:$K$29,"Pass")-COUNTIFS('Phase 1B'!$E$5:$E$29,"P1",'Phase 1B'!$K$5:$K$29,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1B",'Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1B",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1B",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")+COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1B",'Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1B",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1B",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
         <v/>
       </c>
       <c r="I6" s="11">
@@ -6869,31 +7113,31 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTA('Phase 1C'!$A$5:$A$40)</f>
+        <f>COUNTA('Phase 1C'!$A$5:$A$43)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIF('Phase 1C'!$K$5:$K$40,"Pass")</f>
+        <f>COUNTIF('Phase 1C'!$K$5:$K$43,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIF('Phase 1C'!$K$5:$K$40,"Fail")</f>
+        <f>COUNTIF('Phase 1C'!$K$5:$K$43,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIF('Phase 1C'!$K$5:$K$40,"Blocked")</f>
+        <f>COUNTIF('Phase 1C'!$K$5:$K$43,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIF('Phase 1C'!$K$5:$K$40,"N/A")</f>
+        <f>COUNTIF('Phase 1C'!$K$5:$K$43,"N/A")</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>COUNTIF('Phase 1C'!$K$5:$K$40,"Not run")</f>
+        <f>COUNTIF('Phase 1C'!$K$5:$K$43,"Not run")</f>
         <v/>
       </c>
       <c r="H7" s="5">
-        <f>COUNTIFS('Phase 1C'!$E$5:$E$40,"P1")-COUNTIFS('Phase 1C'!$E$5:$E$40,"P1",'Phase 1C'!$K$5:$K$40,"Pass")-COUNTIFS('Phase 1C'!$E$5:$E$40,"P1",'Phase 1C'!$K$5:$K$40,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")</f>
+        <f>COUNTIFS('Phase 1C'!$E$5:$E$43,"P1")-COUNTIFS('Phase 1C'!$E$5:$E$43,"P1",'Phase 1C'!$K$5:$K$43,"Pass")-COUNTIFS('Phase 1C'!$E$5:$E$43,"P1",'Phase 1C'!$K$5:$K$43,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1C",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1C",'Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1C",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1C",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")+COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1C",'Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1C",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1C",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -6943,64 +7187,260 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>COUNTA('Regression'!$A$5:$A$10)</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>COUNTIF('Regression'!$K$5:$K$10,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D9" s="5">
+        <f>COUNTIF('Regression'!$K$5:$K$10,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E9" s="5">
+        <f>COUNTIF('Regression'!$K$5:$K$10,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="F9" s="5">
+        <f>COUNTIF('Regression'!$K$5:$K$10,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G9" s="5">
+        <f>COUNTIF('Regression'!$K$5:$K$10,"Not run")</f>
+        <v/>
+      </c>
+      <c r="H9" s="5">
+        <f>COUNTIFS('Regression'!$E$5:$E$10,"P1")-COUNTIFS('Regression'!$E$5:$E$10,"P1",'Regression'!$K$5:$K$10,"Pass")-COUNTIFS('Regression'!$E$5:$E$10,"P1",'Regression'!$K$5:$K$10,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Already counted in the release gates above — not added again below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>COUNTA('Non-functional'!$A$5:$A$20)</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>COUNTIF('Non-functional'!$K$5:$K$20,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>COUNTIF('Non-functional'!$K$5:$K$20,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>COUNTIF('Non-functional'!$K$5:$K$20,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>COUNTIF('Non-functional'!$K$5:$K$20,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>COUNTIF('Non-functional'!$K$5:$K$20,"Not run")</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
+        <f>COUNTIFS('Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Already counted in the release gates above — not added again below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>End-to-end journeys</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>COUNTA('Use Case Coverage'!$A$5:$A$24)</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>COUNTIF('Use Case Coverage'!$K$5:$K$24,"Pass")</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>COUNTIF('Use Case Coverage'!$K$5:$K$24,"Fail")</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>COUNTIF('Use Case Coverage'!$K$5:$K$24,"Blocked")</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>COUNTIF('Use Case Coverage'!$K$5:$K$24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>COUNTIF('Use Case Coverage'!$K$5:$K$24,"Not run")</f>
+        <v/>
+      </c>
+      <c r="H11" s="5">
+        <f>COUNTIFS('Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>Already counted in the release gates above — not added again below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
           <t>Phase 1 programme</t>
         </is>
       </c>
-      <c r="B9" s="13">
-        <f>SUM(B5:B8)</f>
+      <c r="B12" s="15">
+        <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C9" s="13">
-        <f>SUM(C5:C8)</f>
+      <c r="C12" s="15">
+        <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D9" s="13">
-        <f>SUM(D5:D8)</f>
+      <c r="D12" s="15">
+        <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E9" s="13">
-        <f>SUM(E5:E8)</f>
+      <c r="E12" s="15">
+        <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F9" s="13">
-        <f>SUM(F5:F8)</f>
+      <c r="F12" s="15">
+        <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G9" s="13">
-        <f>SUM(G5:G8)</f>
+      <c r="G12" s="15">
+        <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H12" s="15">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="14">
-        <f>IF(H9=0,"Entire Phase 1 clear","Blocked — "&amp;H9&amp;" P1 outstanding across the programme")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>N/A hygiene</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>N/A without a waiver approver</t>
-        </is>
-      </c>
-      <c r="B12" s="17">
-        <f>(COUNTIFS('Phase 1A'!$K$5:$K$58,"N/A")-COUNTIFS('Phase 1A'!$K$5:$K$58,"N/A",'Phase 1A'!$S$5:$S$58,"&lt;&gt;"))+(COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A")-COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A",'Phase 1B'!$S$5:$S$29,"&lt;&gt;"))+(COUNTIFS('Phase 1C'!$K$5:$K$40,"N/A")-COUNTIFS('Phase 1C'!$K$5:$K$40,"N/A",'Phase 1C'!$S$5:$S$40,"&lt;&gt;"))+(COUNTIFS('Regression'!$K$5:$K$10,"N/A")-COUNTIFS('Regression'!$K$5:$K$10,"N/A",'Regression'!$S$5:$S$10,"&lt;&gt;"))</f>
+      <c r="I12" s="16">
+        <f>IF(H12=0,"Entire Phase 1 clear","Blocked — "&amp;H12&amp;" P1 outstanding across the programme")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Every N/A must carry a reason in Notes and an approver in 'Waiver approved by'.</t>
+          <t>Totals count each population once. P1 blocking sums the three release gates plus recipe coverage — regression, non-functional and journeys are inside those gates already.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>N/A hygiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>N/A missing a reason, an approver, or both</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>(COUNTIFS('Phase 1A'!$K$5:$K$75,"N/A")-COUNTIFS('Phase 1A'!$K$5:$K$75,"N/A",'Phase 1A'!$S$5:$S$75,"&lt;&gt;",'Phase 1A'!$V$5:$V$75,"&lt;&gt;"))+(COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A")-COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A",'Phase 1B'!$S$5:$S$29,"&lt;&gt;",'Phase 1B'!$V$5:$V$29,"&lt;&gt;"))+(COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A")-COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A",'Phase 1C'!$S$5:$S$43,"&lt;&gt;",'Phase 1C'!$V$5:$V$43,"&lt;&gt;"))+(COUNTIFS('Regression'!$K$5:$K$10,"N/A")-COUNTIFS('Regression'!$K$5:$K$10,"N/A",'Regression'!$S$5:$S$10,"&lt;&gt;",'Regression'!$V$5:$V$10,"&lt;&gt;"))+(COUNTIFS('Non-functional'!$K$5:$K$20,"N/A")-COUNTIFS('Non-functional'!$K$5:$K$20,"N/A",'Non-functional'!$S$5:$S$20,"&lt;&gt;",'Non-functional'!$V$5:$V$20,"&lt;&gt;"))+(COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A")-COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A",'Use Case Coverage'!$S$5:$S$24,"&lt;&gt;",'Use Case Coverage'!$V$5:$V$24,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Every N/A needs a reason in Notes AND a name in 'Waiver approved by'. This counts any missing either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>What is counted</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Core functional cases (Phase 1A + 1B + 1C)</t>
+        </is>
+      </c>
+      <c r="B20" s="19">
+        <f>COUNTA('Phase 1A'!$A$5:$A$75)+COUNTA('Phase 1B'!$A$5:$A$29)+COUNTA('Phase 1C'!$A$5:$A$43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Regression cases</t>
+        </is>
+      </c>
+      <c r="B21" s="19">
+        <f>COUNTA(Regression!$A$5:$A$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Non-functional cases</t>
+        </is>
+      </c>
+      <c r="B22" s="19">
+        <f>COUNTA('Non-functional'!$A$5:$A$20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>End-to-end journeys</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>COUNTA('Use Case Coverage'!$A$5:$A$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Recipe matrix checks</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Five separate populations. Quoting only the first understates the plan.</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7040,7 +7480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extracted from §A14 of the PRD. Each release has its own gate; blocking items stop that release only.</t>
+          <t>Extracted from §A15 of the PRD. Each release has its own gate; blocking items stop that release only.</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7562,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7162,7 +7602,7 @@
           <t>Product + CTO</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7202,7 +7642,7 @@
           <t>Product + Eng</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7242,7 +7682,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7282,7 +7722,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7322,7 +7762,7 @@
           <t>Product + Design</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7362,7 +7802,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7402,7 +7842,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7442,7 +7882,7 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7482,7 +7922,7 @@
           <t>Product + Eng</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7562,7 +8002,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7602,7 +8042,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7642,7 +8082,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7682,7 +8122,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7722,7 +8162,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7749,20 +8189,20 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>All eight precedence rules, each proven in isolation.</t>
+          <t>Every route into a quote opens the same dedicated quote workspace, and the global CRM navigation is replaced by the quote's own.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7789,20 +8229,20 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Each of the seven quote-inclusion clauses proven to exclude.</t>
+          <t>The quote workspace shows quote identity, issuing company, linked deal, deal stage and option position, with working navigation back to the list and to the deal.</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
+          <t>Engineering + Design</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7829,20 +8269,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Both revision flags tested in all four combinations.</t>
+          <t>All Companies shows the owning company column and selecting one company hides it. Counts, search, grouping and rows respect both the permission and the filter.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7869,20 +8309,20 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>An event carrying another account's identifiers is rejected.</t>
+          <t>Link, Add option, Switch Deal and Unlink use explicit dialogues, inherit the required records and write audit history.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7909,20 +8349,20 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Flags</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Site Ready custom stage hidden until Phase 2.</t>
+          <t>A quote cannot be silently linked to a deal owned by another company. A cross-company exception requires an explicit permission and a confirmation the user sees.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
+          <t>Engineering + Security</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7949,20 +8389,20 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Flags</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Commit Forecast and Stage-weighted views hidden until Phase 2.</t>
+          <t>All eight precedence rules, each proven in isolation.</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -7989,20 +8429,20 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Handoff</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Conflict register (§C1) signed off, every row resolved or explicitly deferred.</t>
+          <t>Each of the seven quote-inclusion clauses proven to exclude.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8029,22 +8469,22 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Handoff</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Margin definition written down: what each of the four figures includes.</t>
+          <t>Both revision flags tested in all four combinations.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Track</t>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
@@ -8064,25 +8504,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>D7 — whose approval threshold applies on a high-value quote.</t>
+          <t>An event carrying another account's identifiers is rejected.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8104,25 +8544,25 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>One shared description of a flow, with versions stored server-side. Browser storage does not satisfy this.</t>
+          <t>Quote-list row, options popover, deal bridge and a newly created option all reach the same workspace holding the correct record.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8144,25 +8584,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Recipe settings can be changed without opening the canvas.</t>
+          <t>Company column visibility, counts, filters, Group by Deal and empty states proven for All Companies and for each permitted company.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8184,25 +8624,25 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Every recipe carries a company scope, visible everywhere it is listed.</t>
+          <t>Create, link, switch and unlink proven for linked, unlinked, cross-company, Won, cancelled and deleted quotes.</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8224,25 +8664,25 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Timed recipes have a real work queue: persistence, worker, working days, timezone, cancellation when a record leaves the stage.</t>
+          <t>Multiple-option acceptance resolves one winner, the sibling outcomes, the deal stage, engagement counts, activity and invoice idempotency.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8264,25 +8704,25 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Flags</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Replaying the same event creates nothing twice, for every action type.</t>
+          <t>Site Ready custom stage hidden until Phase 2.</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8304,25 +8744,25 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Flags</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Work already in flight finishes on the version it started with.</t>
+          <t>Commit Forecast and Stage-weighted views hidden until Phase 2.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8344,25 +8784,25 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Handoff</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Only one change order can be open per quote.</t>
+          <t>Conflict register (§C1) signed off, every row resolved or explicitly deferred.</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8384,7 +8824,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -8394,7 +8834,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>All twelve recipes are defined and configurable. A timed recipe cannot be switched on until the production work queue exists.</t>
+          <t>Margin definition written down: what each of the four figures includes.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -8402,9 +8842,9 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>Blocking</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Track</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -8424,7 +8864,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Phase 1B</t>
+          <t>Phase 1A</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -8434,12 +8874,12 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Event-driven recipes ship first. Timed recipes stay unavailable, not merely inactive, until the queue lands.</t>
+          <t>Product copy defines quote, option, revision, alternative group, linked deal, issuing company, Rejected, Cancelled, Expired, Lost and Archived consistently.</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -8464,25 +8904,25 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Decisions</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>The block list is built from one shared source. No per-stage hard-coded lists, and placement never used as a permission key (FR-33).</t>
+          <t>D7 — whose approval threshold applies on a high-value quote.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8504,7 +8944,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -8514,7 +8954,7 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Draft, optional test and publish, with publishing blocked only by a real conflict.</t>
+          <t>One shared description of a flow, with versions stored server-side. Browser storage does not satisfy this.</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -8522,7 +8962,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8544,7 +8984,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -8554,7 +8994,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Required-work gate collects every outstanding item and resumes the exact original action.</t>
+          <t>Recipe settings can be changed without opening the canvas.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -8562,7 +9002,7 @@
           <t>Engineering</t>
         </is>
       </c>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8584,25 +9024,25 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>The shared core block list is identical in all seven protected stages. Stage-specific quote events and rules appear only where they can genuinely occur.</t>
+          <t>Every recipe carries a company scope, visible everywhere it is listed.</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8624,25 +9064,25 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>A draft or test never changes the live version.</t>
+          <t>Timed recipes have a real work queue: persistence, worker, working days, timezone, cancellation when a record leaves the stage.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="inlineStr">
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -8664,27 +9104,27 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Phase 1C</t>
+          <t>Phase 1B</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Handoff</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>"Open as an editable copy" documented as one-way, with no promise of returning to the simple form.</t>
+          <t>Replaying the same event creates nothing twice, for every action type.</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Track</t>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>Blocking</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
@@ -8696,130 +9136,530 @@
       <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>G-41</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Work already in flight finishes on the version it started with.</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>G-42</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Only one change order can be open per quote.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>G-43</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Handoff</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>All twelve recipes are defined and configurable. A timed recipe cannot be switched on until the production work queue exists.</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>G-44</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Handoff</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Event-driven recipes ship first. Timed recipes stay unavailable, not merely inactive, until the queue lands.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>G-45</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>The block list is built from one shared source. No per-stage hard-coded lists, and placement never used as a permission key (FR-33).</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>G-46</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Draft, optional test and publish, with publishing blocked only by a real conflict.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>G-47</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Required-work gate collects every outstanding item and resumes the exact original action.</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>G-48</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>The shared core block list is identical in all seven protected stages. Stage-specific quote events and rules appear only where they can genuinely occur.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>G-49</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>A draft or test never changes the live version.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>G-50</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Handoff</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>"Open as an editable copy" documented as one-way, with no promise of returning to the simple form.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Gate by release</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>Blocking outstanding</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="B48" s="5">
-        <f>COUNTIF($B$5:$B$44,"Phase 1A")</f>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="B58" s="5">
+        <f>COUNTIF($B$5:$B$54,"Phase 1A")</f>
         <v/>
       </c>
-      <c r="C48" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1A",$H$5:$H$44,"Done")</f>
+      <c r="C58" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1A",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="D48" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1A",$F$5:$F$44,"Blocking")-COUNTIFS($B$5:$B$44,"Phase 1A",$F$5:$F$44,"Blocking",$H$5:$H$44,"Done")</f>
+      <c r="D58" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1A",$F$5:$F$54,"Blocking")-COUNTIFS($B$5:$B$54,"Phase 1A",$F$5:$F$54,"Blocking",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="E48" s="11">
-        <f>IF(D48=0,"Gate clear","Blocked — "&amp;D48&amp;" outstanding")</f>
+      <c r="E58" s="11">
+        <f>IF(D58=0,"Gate clear","Blocked — "&amp;D58&amp;" outstanding")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Phase 1B</t>
         </is>
       </c>
-      <c r="B49" s="5">
-        <f>COUNTIF($B$5:$B$44,"Phase 1B")</f>
+      <c r="B59" s="5">
+        <f>COUNTIF($B$5:$B$54,"Phase 1B")</f>
         <v/>
       </c>
-      <c r="C49" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1B",$H$5:$H$44,"Done")</f>
+      <c r="C59" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1B",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="D49" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1B",$F$5:$F$44,"Blocking")-COUNTIFS($B$5:$B$44,"Phase 1B",$F$5:$F$44,"Blocking",$H$5:$H$44,"Done")</f>
+      <c r="D59" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1B",$F$5:$F$54,"Blocking")-COUNTIFS($B$5:$B$54,"Phase 1B",$F$5:$F$54,"Blocking",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="E49" s="11">
-        <f>IF(D49=0,"Gate clear","Blocked — "&amp;D49&amp;" outstanding")</f>
+      <c r="E59" s="11">
+        <f>IF(D59=0,"Gate clear","Blocked — "&amp;D59&amp;" outstanding")</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Phase 1C</t>
         </is>
       </c>
-      <c r="B50" s="5">
-        <f>COUNTIF($B$5:$B$44,"Phase 1C")</f>
+      <c r="B60" s="5">
+        <f>COUNTIF($B$5:$B$54,"Phase 1C")</f>
         <v/>
       </c>
-      <c r="C50" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1C",$H$5:$H$44,"Done")</f>
+      <c r="C60" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1C",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="D50" s="5">
-        <f>COUNTIFS($B$5:$B$44,"Phase 1C",$F$5:$F$44,"Blocking")-COUNTIFS($B$5:$B$44,"Phase 1C",$F$5:$F$44,"Blocking",$H$5:$H$44,"Done")</f>
+      <c r="D60" s="5">
+        <f>COUNTIFS($B$5:$B$54,"Phase 1C",$F$5:$F$54,"Blocking")-COUNTIFS($B$5:$B$54,"Phase 1C",$F$5:$F$54,"Blocking",$H$5:$H$54,"Done")</f>
         <v/>
       </c>
-      <c r="E50" s="11">
-        <f>IF(D50=0,"Gate clear","Blocked — "&amp;D50&amp;" outstanding")</f>
+      <c r="E60" s="11">
+        <f>IF(D60=0,"Gate clear","Blocked — "&amp;D60&amp;" outstanding")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Rows missing Owner or Target date</t>
         </is>
       </c>
-      <c r="B51" s="17">
-        <f>COUNTIF($G$5:$G$44,"")+COUNTIF($I$5:$I$44,"")</f>
+      <c r="B61" s="19">
+        <f>COUNTIF($G$5:$G$54,"")+COUNTIF($I$5:$I$54,"")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Every gate row needs a named owner and a target date before the release is planned.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J44"/>
-  <conditionalFormatting sqref="H5:H44">
+  <autoFilter ref="A4:J54"/>
+  <conditionalFormatting sqref="H5:H54">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -8834,7 +9674,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,In progress,Done,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8848,7 +9688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8969,10 +9809,10 @@
         </is>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-08",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-08",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>GAP: the transition is stated in §A6 and tested, but no functional requirement carries it. Add one, or cite §A6 explicitly.</t>
         </is>
@@ -9032,7 +9872,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>G-17</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -9041,7 +9881,7 @@
         </is>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-14",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-14",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -9064,7 +9904,7 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-15",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-15",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
       <c r="J8" s="6" t="inlineStr"/>
@@ -9087,7 +9927,7 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-16",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-16",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
@@ -9110,7 +9950,7 @@
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-17",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-17",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
@@ -9169,7 +10009,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>G-17</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -9178,10 +10018,10 @@
         </is>
       </c>
       <c r="I12" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$58,MATCH("1A-19",'Phase 1A'!$A$5:$A$58,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-19",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
         <v/>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t>GAP: no FR separates deriving the outcome from supplying the reason. §A6 and §A7 both state it; a requirement should too.</t>
         </is>
@@ -9236,12 +10076,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1C-18</t>
+          <t>1C-21</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>G-36</t>
+          <t>G-46</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -9250,7 +10090,7 @@
         </is>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$40,MATCH("1C-18",'Phase 1C'!$A$5:$A$40,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$43,MATCH("1C-21",'Phase 1C'!$A$5:$A$43,0)),"not found")</f>
         <v/>
       </c>
       <c r="J14" s="6" t="inlineStr"/>
@@ -9309,7 +10149,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>G-35, G-38</t>
+          <t>G-45, G-48</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -9318,7 +10158,7 @@
         </is>
       </c>
       <c r="I16" s="8">
-        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$40,MATCH("1C-06",'Phase 1C'!$A$5:$A$40,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$43,MATCH("1C-06",'Phase 1C'!$A$5:$A$43,0)),"not found")</f>
         <v/>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -9345,7 +10185,7 @@
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8">
-        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$40,MATCH("1C-09",'Phase 1C'!$A$5:$A$40,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$43,MATCH("1C-09",'Phase 1C'!$A$5:$A$43,0)),"not found")</f>
         <v/>
       </c>
       <c r="J17" s="9" t="inlineStr"/>
@@ -9413,7 +10253,7 @@
         </is>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$40,MATCH("1C-08",'Phase 1C'!$A$5:$A$40,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1C'!$K$5:$K$43,MATCH("1C-08",'Phase 1C'!$A$5:$A$43,0)),"not found")</f>
         <v/>
       </c>
       <c r="J19" s="6" t="inlineStr"/>
@@ -9441,38 +10281,265 @@
       </c>
       <c r="J20" s="6" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>A quote and its deal share an owning company. Crossing that boundary needs a permission the user holds and a confirmation they see.</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>FR-51</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>AC-QS-10</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>1A-63</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>G-14, G-21</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="I21" s="8">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-63",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Every route into a quote reaches the same dedicated workspace. No route falls back to the old quote summary.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>FR-42, FR-43</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>AC-QS-01, AC-QS-02</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>1A-58</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>G-17, G-26</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="I22" s="5">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-58",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>1A-60</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-60",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Link, add option, switch and unlink never change the owning company, the customer or an accepted outcome, and each writes an audit event.</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>FR-50, FR-52, FR-53, FR-55</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>AC-QS-08, AC-QS-12, AC-QS-13</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>1A-61</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>G-20</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="I24" s="8">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-61",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>1A-66</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-66",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>1A-67</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-67",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>1A-68</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8">
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-68",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <v/>
+      </c>
+      <c r="J27" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Linked cases passing</t>
         </is>
       </c>
-      <c r="C22" s="15">
-        <f>COUNTIF(I5:I20,"Pass")&amp;" of "&amp;COUNTA(I5:I20)</f>
+      <c r="C29" s="17">
+        <f>COUNTIF(I5:I27,"Pass")&amp;" of "&amp;COUNTA(I5:I27)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Requirement gaps</t>
         </is>
       </c>
-      <c r="C23" s="24">
-        <f>COUNTIF(J5:J20,"GAP*")&amp;" locked rules have no functional requirement"</f>
+      <c r="C30" s="26">
+        <f>COUNTIF(J5:J27,"GAP*")&amp;" locked rules have no functional requirement"</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="25" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>A locked rule is only safe once every linked QA case passes AND its delivery gate item is Done. The two gaps are documentation gaps, not test gaps — both rules are tested.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J20"/>
-  <conditionalFormatting sqref="I5:I20">
+  <autoFilter ref="A4:J27"/>
+  <conditionalFormatting sqref="I5:I27">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -9499,32 +10566,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Use case coverage</t>
+          <t>End-to-end journeys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>End-to-end journeys, each mapped to the granular cases that make it up. Coverage is live: it reads those cases' results.</t>
+          <t>Each journey is a test in its own right: run it start to finish and record the result in Status. The three columns on the right are a separate signal — they read the granular cases behind the journey. Those cases passing does NOT mean the journey was ever run end to end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fill in from Status onwards. Everything to the left describes the test.</t>
         </is>
       </c>
     </row>
@@ -9536,855 +10625,1764 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Use case</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>Applies from</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Persona</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Journey</t>
+          <t>Pri</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Test IDs</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Precondition</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Passing</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Traces to</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Actual result</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Browser / device</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Test data</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Evidence link</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Waiver approved by</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Component cases</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Component passing</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>Component coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>UC-01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Lead to first quote</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>New Lead → duplicate check → customer linked → convert → Deal in Qualified → create first quote → In Progress</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>One Deal exists in Qualified with the matched customer linked, and it moves to In Progress the moment the first quote is created. No second customer record was made.</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>1A-01, 1A-02, 1A-08</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-01",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-02",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-08",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X5" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-01",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-02",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-08",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I5" s="4">
-        <f>IF(H5=G5,"Fully covered",IF(H5=0,"Not started","Partial — "&amp;H5&amp;" of "&amp;G5)</f>
+      <c r="Y5" s="6">
+        <f>IF(X5=W5,"All parts pass",IF(X5=0,"No parts pass yet","Partial — "&amp;X5&amp;" of "&amp;W5))</f>
         <v/>
       </c>
-      <c r="J5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>UC-02</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Full review path</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Sales + Reviewer</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales + Reviewer, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>In Progress → submit → In Review → pass → Passed Review → send → Sent</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>The Deal reaches Sent by way of In Review and Passed Review, and the history names who submitted it, who passed it and who sent it.</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>1A-09, 1A-10, 1A-11</t>
         </is>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="8" t="inlineStr"/>
+      <c r="V6" s="9" t="inlineStr"/>
+      <c r="W6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-09",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-10",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-11",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X6" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-09",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-10",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-11",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I6" s="7">
-        <f>IF(H6=G6,"Fully covered",IF(H6=0,"Not started","Partial — "&amp;H6&amp;" of "&amp;G6)</f>
+      <c r="Y6" s="9">
+        <f>IF(X6=W6,"All parts pass",IF(X6=0,"No parts pass yet","Partial — "&amp;X6&amp;" of "&amp;W6))</f>
         <v/>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>UC-03</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>No-review path</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Review disabled → In Progress → send → Sent, skipping both review stages</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>The Deal moves straight from In Progress to Sent. Neither review stage appears on the board or in the history.</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>1A-12</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-12",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X7" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-12",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I7" s="4">
-        <f>IF(H7=G7,"Fully covered",IF(H7=0,"Not started","Partial — "&amp;H7&amp;" of "&amp;G7)</f>
+      <c r="Y7" s="6">
+        <f>IF(X7=W7,"All parts pass",IF(X7=0,"No parts pass yet","Partial — "&amp;X7&amp;" of "&amp;W7))</f>
         <v/>
       </c>
-      <c r="J7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>UC-04</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Changes requested</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Run by Reviewer, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>In Review → changes requested → back to In Progress → resubmit</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>The Deal returns to In Progress carrying the reviewer's comments, and resubmitting takes it back to In Review.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>1A-13, 1A-09</t>
         </is>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="8" t="inlineStr"/>
+      <c r="V8" s="9" t="inlineStr"/>
+      <c r="W8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-13",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-09",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X8" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-13",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-09",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I8" s="7">
-        <f>IF(H8=G8,"Fully covered",IF(H8=0,"Not started","Partial — "&amp;H8&amp;" of "&amp;G8)</f>
+      <c r="Y8" s="9">
+        <f>IF(X8=W8,"All parts pass",IF(X8=0,"No parts pass yet","Partial — "&amp;X8&amp;" of "&amp;W8))</f>
         <v/>
       </c>
-      <c r="J8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>UC-05</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Client engagement</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Three quotes sent → client opens two → Deal card shows 2 of 3 viewed</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>The Deal card reads 2 of 3 viewed. The unopened quote counts in the denominator and not as viewed.</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>1A-31, 1A-30, 1A-32</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-31",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-30",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-32",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X9" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-31",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-30",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-32",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I9" s="4">
-        <f>IF(H9=G9,"Fully covered",IF(H9=0,"Not started","Partial — "&amp;H9&amp;" of "&amp;G9)</f>
+      <c r="Y9" s="6">
+        <f>IF(X9=W9,"All parts pass",IF(X9=0,"No parts pass yet","Partial — "&amp;X9&amp;" of "&amp;W9))</f>
         <v/>
       </c>
-      <c r="J9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>UC-06</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Win the deal</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Alternative group of three → accept one → siblings rejected → Deal Won → value locked</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Accepting one quote makes the Deal Won, marks its two siblings rejected, and sets the signed value to the accepted quote alone.</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>1A-16, 1A-14, 1A-45</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="8" t="inlineStr"/>
+      <c r="V10" s="9" t="inlineStr"/>
+      <c r="W10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-16",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-14",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-45",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X10" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-16",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-14",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-45",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I10" s="7">
-        <f>IF(H10=G10,"Fully covered",IF(H10=0,"Not started","Partial — "&amp;H10&amp;" of "&amp;G10)</f>
+      <c r="Y10" s="9">
+        <f>IF(X10=W10,"All parts pass",IF(X10=0,"No parts pass yet","Partial — "&amp;X10&amp;" of "&amp;W10))</f>
         <v/>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>UC-07</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Lose the deal</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>All quotes expire → Lost derived → Sales supplies the loss reason</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>The Deal shows Lost without anyone setting it, and the reason Sales entered is stored against it.</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>1A-19</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-19",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X11" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-19",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I11" s="4">
-        <f>IF(H11=G11,"Fully covered",IF(H11=0,"Not started","Partial — "&amp;H11&amp;" of "&amp;G11)</f>
+      <c r="Y11" s="6">
+        <f>IF(X11=W11,"All parts pass",IF(X11=0,"No parts pass yet","Partial — "&amp;X11&amp;" of "&amp;W11))</f>
         <v/>
       </c>
-      <c r="J11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>UC-08</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Work called off</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>All quotes cancelled → Deal Archived, not Lost</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>The Deal shows Archived. It is not Lost and is not counted as a loss anywhere.</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>1A-18</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="9" t="inlineStr"/>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="8" t="inlineStr"/>
+      <c r="V12" s="9" t="inlineStr"/>
+      <c r="W12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-18",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X12" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-18",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I12" s="7">
-        <f>IF(H12=G12,"Fully covered",IF(H12=0,"Not started","Partial — "&amp;H12&amp;" of "&amp;G12)</f>
+      <c r="Y12" s="9">
+        <f>IF(X12=W12,"All parts pass",IF(X12=0,"No parts pass yet","Partial — "&amp;X12&amp;" of "&amp;W12))</f>
         <v/>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+    </row>
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>UC-09</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Additive versus competing</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Two independent quotes add up; two grouped quotes compete</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>The two independent quotes both add into the Deal value; of the two grouped quotes only the winner counts.</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>1A-34, 1A-35, 1A-37</t>
         </is>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-34",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-35",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-37",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X13" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-34",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-35",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-37",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I13" s="4">
-        <f>IF(H13=G13,"Fully covered",IF(H13=0,"Not started","Partial — "&amp;H13&amp;" of "&amp;G13)</f>
+      <c r="Y13" s="6">
+        <f>IF(X13=W13,"All parts pass",IF(X13=0,"No parts pass yet","Partial — "&amp;X13&amp;" of "&amp;W13))</f>
         <v/>
       </c>
-      <c r="J13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    </row>
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>UC-10</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Vary sold work</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Sales + Finance</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales + Finance, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Accepted quote → raise change order → client signs → value updated, stage unchanged</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>The Deal value rises by the signed change order while the stage stays Won, and the base value and the change order remain visible separately.</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>1A-38, 1A-40, 1A-42</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="8" t="inlineStr"/>
+      <c r="V14" s="9" t="inlineStr"/>
+      <c r="W14" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-38",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-40",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-42",'Phase 1A'!$K$5:$K$58,"Pass")</f>
+      <c r="X14" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-38",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-40",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-42",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I14" s="7">
-        <f>IF(H14=G14,"Fully covered",IF(H14=0,"Not started","Partial — "&amp;H14&amp;" of "&amp;G14)</f>
+      <c r="Y14" s="9">
+        <f>IF(X14=W14,"All parts pass",IF(X14=0,"No parts pass yet","Partial — "&amp;X14&amp;" of "&amp;W14))</f>
         <v/>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+    </row>
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>UC-11</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Multi-company working</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1A</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Run by Manager, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Audio Vision manager sees permitted companies only; scoped Automation runs for one branch</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>The manager sees Deals for permitted companies only, and the scoped Automation runs for that branch's Deals and no others.</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>1A-47, 1B-04</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$58,"1A-47",'Phase 1A'!$K$5:$K$58,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-04",'Phase 1B'!$K$5:$K$29,"Pass")</f>
+      <c r="X15" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-47",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-04",'Phase 1B'!$K$5:$K$29,"Pass")</f>
         <v/>
       </c>
-      <c r="I15" s="4">
-        <f>IF(H15=G15,"Fully covered",IF(H15=0,"Not started","Partial — "&amp;H15&amp;" of "&amp;G15)</f>
+      <c r="Y15" s="6">
+        <f>IF(X15=W15,"All parts pass",IF(X15=0,"No parts pass yet","Partial — "&amp;X15&amp;" of "&amp;W15))</f>
         <v/>
       </c>
-      <c r="J15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+    </row>
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>UC-12</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Switch on a recipe</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1B</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Run by Admin, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Choose a recipe → set owner, days and scope → activate → it fires and writes to the Deal card</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>The recipe is live with the chosen owner, days and scope, fires on its trigger, and its result reaches the Deal card, not only the history.</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>1B-01, 1B-02, 1B-20</t>
         </is>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="8" t="inlineStr"/>
+      <c r="V16" s="9" t="inlineStr"/>
+      <c r="W16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="8">
+      <c r="X16" s="8">
         <f>COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-01",'Phase 1B'!$K$5:$K$29,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-02",'Phase 1B'!$K$5:$K$29,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-20",'Phase 1B'!$K$5:$K$29,"Pass")</f>
         <v/>
       </c>
-      <c r="I16" s="7">
-        <f>IF(H16=G16,"Fully covered",IF(H16=0,"Not started","Partial — "&amp;H16&amp;" of "&amp;G16)</f>
+      <c r="Y16" s="9">
+        <f>IF(X16=W16,"All parts pass",IF(X16=0,"No parts pass yet","Partial — "&amp;X16&amp;" of "&amp;W16))</f>
         <v/>
       </c>
-      <c r="J16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+    </row>
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>UC-13</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Chase a sent quote</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1B</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Quote sent → wait three working days → follow-up note created and visible</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Three working days after the quote is sent, a follow-up note exists on the Deal, attributed to the recipe and visible on the card.</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>1B-09, 1B-21</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="5">
+      <c r="X17" s="5">
         <f>COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-09",'Phase 1B'!$K$5:$K$29,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-21",'Phase 1B'!$K$5:$K$29,"Pass")</f>
         <v/>
       </c>
-      <c r="I17" s="4">
-        <f>IF(H17=G17,"Fully covered",IF(H17=0,"Not started","Partial — "&amp;H17&amp;" of "&amp;G17)</f>
+      <c r="Y17" s="6">
+        <f>IF(X17=W17,"All parts pass",IF(X17=0,"No parts pass yet","Partial — "&amp;X17&amp;" of "&amp;W17))</f>
         <v/>
       </c>
-      <c r="J17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>UC-14</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1B</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>High-value approval</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1B</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Sales + Approver</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales + Approver, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Quote passes review above threshold → approval note raised to the approver</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>An approval note is raised to the named approver. The same quote below the threshold raises nothing.</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>1B-16, 1B-17</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr"/>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="8" t="inlineStr"/>
+      <c r="V18" s="9" t="inlineStr"/>
+      <c r="W18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="8">
+      <c r="X18" s="8">
         <f>COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-16",'Phase 1B'!$K$5:$K$29,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-17",'Phase 1B'!$K$5:$K$29,"Pass")</f>
         <v/>
       </c>
-      <c r="I18" s="7">
-        <f>IF(H18=G18,"Fully covered",IF(H18=0,"Not started","Partial — "&amp;H18&amp;" of "&amp;G18)</f>
+      <c r="Y18" s="9">
+        <f>IF(X18=W18,"All parts pass",IF(X18=0,"No parts pass yet","Partial — "&amp;X18&amp;" of "&amp;W18))</f>
         <v/>
       </c>
-      <c r="J18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+    </row>
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>UC-15</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Draft to publish</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Run by Admin, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Open → edit → save draft → test → validate → publish → history recorded</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>The published version is live, the previous version is retained, and the history records who published what and when.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>1C-12, 1C-17, 1C-23, 1C-33</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="6" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" s="5">
+        <f>COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-12",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-17",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-23",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-33",'Phase 1C'!$K$5:$K$43,"Pass")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="6">
+        <f>IF(X19=W19,"All parts pass",IF(X19=0,"No parts pass yet","Partial — "&amp;X19&amp;" of "&amp;W19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>UC-16</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Phase 1C</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Open → edit → save draft → test → validate → publish → history recorded</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1C-12, 1C-16, 1C-20, 1C-30</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Blocked publish</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Run by Admin, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Introduce a conflict → publishing refused with the step named → fix → publish succeeds</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Publishing is refused with the offending step named; after the fix the same publish succeeds unchanged.</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>1C-24, 1C-23</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="9" t="inlineStr"/>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="8" t="inlineStr"/>
+      <c r="V20" s="9" t="inlineStr"/>
+      <c r="W20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" s="8">
+        <f>COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-24",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-23",'Phase 1C'!$K$5:$K$43,"Pass")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="9">
+        <f>IF(X20=W20,"All parts pass",IF(X20=0,"No parts pass yet","Partial — "&amp;X20&amp;" of "&amp;W20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>UC-17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Required work before a move</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Attempt a stage move → outstanding items listed → resolve inline → original action resumes</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Every outstanding item is listed, each is resolvable without leaving the dialog, and the original stage move completes once the list is empty.</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>1C-36, 1C-35</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" s="5">
+        <f>COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-36",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-35",'Phase 1C'!$K$5:$K$43,"Pass")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="6">
+        <f>IF(X21=W21,"All parts pass",IF(X21=0,"No parts pass yet","Partial — "&amp;X21&amp;" of "&amp;W21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>UC-18</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1C</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Right pipeline every time</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Run by Admin, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Deal on a non-Sales pipeline → open its Automations from the Deal page → correct pipeline opens</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Opening Automations from the Deal lands on that Deal's own pipeline every time, never the Sales default.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>1C-05, 1C-03, 1C-04</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="9" t="inlineStr"/>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="8" t="inlineStr"/>
+      <c r="V22" s="9" t="inlineStr"/>
+      <c r="W22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" s="8">
+        <f>COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-05",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-03",'Phase 1C'!$K$5:$K$43,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$43,"1C-04",'Phase 1C'!$K$5:$K$43,"Pass")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="9">
+        <f>IF(X22=W22,"All parts pass",IF(X22=0,"No parts pass yet","Partial — "&amp;X22&amp;" of "&amp;W22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>UC-19</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Every door, one workspace</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Open a quote from all five routes → same workspace, same record → navigate it → share its address → return</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>All five routes reach the dedicated workspace holding the clicked record, the CRM sidebar never reappears, every navigation item works, and the quote's address reopens it in a fresh session.</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>1A-58, 1A-59, 1A-60, 1A-69</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="5">
-        <f>COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-12",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-16",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-20",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-30",'Phase 1C'!$K$5:$K$40,"Pass")</f>
+      <c r="X23" s="5">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-58",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-59",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-60",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-69",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I19" s="4">
-        <f>IF(H19=G19,"Fully covered",IF(H19=0,"Not started","Partial — "&amp;H19&amp;" of "&amp;G19)</f>
+      <c r="Y23" s="6">
+        <f>IF(X23=W23,"All parts pass",IF(X23=0,"No parts pass yet","Partial — "&amp;X23&amp;" of "&amp;W23))</f>
         <v/>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>UC-16</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Blocked publish</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1C</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Introduce a conflict → publishing refused with the step named → fix → publish succeeds</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>1C-21, 1C-20</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="8">
-        <f>COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-21",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-20",'Phase 1C'!$K$5:$K$40,"Pass")</f>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Group the work, then change it</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Run by Sales, on staging with the Phase 1 test data in place.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Link a loose quote → add an option → switch it to another deal → unlink → records stay whole throughout</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Each relationship action states what it changes before it changes it, both option counts stay truthful throughout, every step writes an audit event, and no quote or deal is left orphaned or duplicated.</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>1A-61, 1A-64, 1A-66, 1A-68</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="9" t="inlineStr"/>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="8" t="inlineStr"/>
+      <c r="V24" s="9" t="inlineStr"/>
+      <c r="W24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="X24" s="8">
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-61",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-64",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-66",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-68",'Phase 1A'!$K$5:$K$75,"Pass")</f>
         <v/>
       </c>
-      <c r="I20" s="7">
-        <f>IF(H20=G20,"Fully covered",IF(H20=0,"Not started","Partial — "&amp;H20&amp;" of "&amp;G20)</f>
+      <c r="Y24" s="9">
+        <f>IF(X24=W24,"All parts pass",IF(X24=0,"No parts pass yet","Partial — "&amp;X24&amp;" of "&amp;W24))</f>
         <v/>
       </c>
-      <c r="J20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>UC-17</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Required work before a move</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Phase 1C</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Attempt a stage move → outstanding items listed → resolve inline → original action resumes</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>1C-33, 1C-32</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5">
-        <f>COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-33",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-32",'Phase 1C'!$K$5:$K$40,"Pass")</f>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Journeys passed end to end</t>
+        </is>
+      </c>
+      <c r="D26" s="17">
+        <f>COUNTIF(K5:K24,"Pass")&amp;" of "&amp;COUNTA(K5:K24)</f>
         <v/>
       </c>
-      <c r="I21" s="4">
-        <f>IF(H21=G21,"Fully covered",IF(H21=0,"Not started","Partial — "&amp;H21&amp;" of "&amp;G21)</f>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Journeys whose parts all pass</t>
+        </is>
+      </c>
+      <c r="D27" s="18">
+        <f>COUNTIF(Y5:Y24,"All parts pass")&amp;" of "&amp;COUNTA(Y5:Y24)</f>
         <v/>
       </c>
-      <c r="J21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>UC-18</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Right pipeline every time</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1C</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Deal on a non-Sales pipeline → open its Automations from the Deal page → correct pipeline opens</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>1C-05, 1C-03, 1C-04</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="8">
-        <f>COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-05",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-03",'Phase 1C'!$K$5:$K$40,"Pass")+COUNTIFS('Phase 1C'!$A$5:$A$40,"1C-04",'Phase 1C'!$K$5:$K$40,"Pass")</f>
-        <v/>
-      </c>
-      <c r="I22" s="7">
-        <f>IF(H22=G22,"Fully covered",IF(H22=0,"Not started","Partial — "&amp;H22&amp;" of "&amp;G22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="9" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Journeys fully covered</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>COUNTIF(I5:I22,"Fully covered")&amp;" of "&amp;COUNTA(I5:I22)</f>
-        <v/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>A journey is only proven by its own Status. The second line is a readiness hint, not evidence.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J22"/>
+  <autoFilter ref="A4:Y24"/>
+  <conditionalFormatting sqref="K5:K24">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="7">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Not run"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="K5:K24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Manual,Automated,Both"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10395,15 +12393,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
@@ -10981,7 +12979,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11049,7 +13047,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -11117,7 +13115,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11185,7 +13183,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -11253,7 +13251,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11321,7 +13319,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -11389,7 +13387,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11457,7 +13455,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -11525,7 +13523,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11593,7 +13591,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -11661,7 +13659,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11729,7 +13727,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -11797,7 +13795,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11865,7 +13863,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -11933,7 +13931,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12001,7 +13999,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -12069,7 +14067,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12137,7 +14135,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -12205,7 +14203,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12273,7 +14271,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -12341,7 +14339,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12409,7 +14407,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -12477,7 +14475,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Resolver</t>
+          <t>Quote status decides Deal stage</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14227,9 +16225,1165 @@
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="9" t="inlineStr"/>
     </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>1A-55</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Quotes across three permitted companies; All Companies selected.</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Read the list.</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Every row identifies its issuing company by a readable short name, and the full name is obtainable without opening the quote.</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>FR-46 / AC-QS-04</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="4" t="inlineStr"/>
+      <c r="S59" s="4" t="inlineStr"/>
+      <c r="T59" s="4" t="inlineStr"/>
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>1A-56</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>The same list, All Companies selected.</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>Select one company.</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>The owning company column disappears. Status counts, search results, pagination totals and rows all narrow to that company alone.</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>FR-46 / AC-QS-05</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr"/>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr"/>
+      <c r="Q60" s="9" t="inlineStr"/>
+      <c r="R60" s="7" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="7" t="inlineStr"/>
+      <c r="U60" s="8" t="inlineStr"/>
+      <c r="V60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>1A-57</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Quotes belonging to several deals.</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Turn on Group by Deal with the company column shown, then with it hidden.</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Group headings and column spans stay aligned in both states, and no quote record changes. Turning it off restores the flat list exactly.</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>FR-48 / AC-QS-06</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr"/>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr"/>
+      <c r="S61" s="4" t="inlineStr"/>
+      <c r="T61" s="4" t="inlineStr"/>
+      <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>1A-58</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>A deal with three quote options.</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Open a quote from all five routes: list row, quote ID in the options popover, option in the linked-deal panel, a newly created option, and a related quote on the Deal.</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>All five open the dedicated quote workspace on the record that was clicked. The global CRM sidebar and top bar are absent every time, and no route falls back to the old quote summary.</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>FR-42, FR-43 / AC-QS-01, AC-QS-02</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="7" t="inlineStr"/>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr"/>
+      <c r="Q62" s="9" t="inlineStr"/>
+      <c r="R62" s="7" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr"/>
+      <c r="T62" s="7" t="inlineStr"/>
+      <c r="U62" s="8" t="inlineStr"/>
+      <c r="V62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>1A-59</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>A quote open in the workspace.</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Open every item in the quote navigation in turn, then return to Summary from each.</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Every item opens and every one returns to Summary. Nothing routes back into the CRM shell.</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>FR-43 / AC-QS-03</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr"/>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="4" t="inlineStr"/>
+      <c r="S63" s="4" t="inlineStr"/>
+      <c r="T63" s="4" t="inlineStr"/>
+      <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>1A-60</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>A quote open in the workspace.</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Copy the browser address, open it in a fresh session as a permitted user, then as a user without that company.</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>The permitted user lands on the same quote in the workspace. The unpermitted user is refused, and nothing about the quote leaks in the refusal.</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>FR-57 / AC-QS-15</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr"/>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr"/>
+      <c r="Q64" s="9" t="inlineStr"/>
+      <c r="R64" s="7" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr"/>
+      <c r="U64" s="8" t="inlineStr"/>
+      <c r="V64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>1A-61</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>An unlinked quote and a compatible deal in the same company.</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Link the quote to the existing deal.</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>The dialogue states what will change before confirmation. Afterwards the quote shows the deal, its derived stage and Option N of M, and the owning company, the customer and any accepted outcome are unchanged.</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>FR-50 / AC-QS-08</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr"/>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="4" t="inlineStr"/>
+      <c r="S65" s="4" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr"/>
+      <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>1A-62</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Two unlinked quotes in the same company.</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Link one to the other.</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>One shared deal grouping results. No duplicate quote is created and neither quote's own record is rewritten.</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>FR-50 / AC-QS-09</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="7" t="inlineStr"/>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr"/>
+      <c r="Q66" s="9" t="inlineStr"/>
+      <c r="R66" s="7" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr"/>
+      <c r="T66" s="7" t="inlineStr"/>
+      <c r="U66" s="8" t="inlineStr"/>
+      <c r="V66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>1A-63</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>A quote in one company and a deal in another.</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Attempt to link them, first as a user without cross-company permission, then as one who has it.</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>The first attempt is refused. The second completes only after a confirmation the user sees, and the exception is recorded.</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>FR-51 / AC-QS-10</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr"/>
+      <c r="Q67" s="6" t="inlineStr"/>
+      <c r="R67" s="4" t="inlineStr"/>
+      <c r="S67" s="4" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr"/>
+      <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>1A-64</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>A deal with one quote option.</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Choose Add option, then create a new option.</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>Nothing is created until confirmation. The new option carries the name supplied and inherits the deal's customer, project, owning company and deal reference. The option count updates and the new quote opens in the workspace.</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>FR-54 / AC-QS-11</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr"/>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr"/>
+      <c r="Q68" s="9" t="inlineStr"/>
+      <c r="R68" s="7" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr"/>
+      <c r="T68" s="7" t="inlineStr"/>
+      <c r="U68" s="8" t="inlineStr"/>
+      <c r="V68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1A-65</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>A deal with one option, and a compatible unlinked quote.</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Choose Add option, then link the existing quote instead of creating one.</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>The existing quote becomes an option on the deal. No duplicate quote is created and the option count reflects the real number.</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>FR-54 / AC-QS-09</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr"/>
+      <c r="Q69" s="6" t="inlineStr"/>
+      <c r="R69" s="4" t="inlineStr"/>
+      <c r="S69" s="4" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr"/>
+      <c r="U69" s="5" t="inlineStr"/>
+      <c r="V69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>1A-66</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>A quote linked to deal A, and a second deal B in the same company.</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Switch the quote to deal B.</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Deal A's option count falls, deal B's rises, and an audit event records the quote, both deals, the actor and the time. Nothing about the quote's own content changes.</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>FR-52, FR-53 / AC-QS-12</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="7" t="inlineStr"/>
+      <c r="Q70" s="9" t="inlineStr"/>
+      <c r="R70" s="7" t="inlineStr"/>
+      <c r="S70" s="7" t="inlineStr"/>
+      <c r="T70" s="7" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr"/>
+      <c r="V70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>1A-67</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>A quote linked to a Won deal.</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Attempt to switch it to another deal.</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>The attempt is refused, or is allowed only through an explicit protected path. Either way the Won outcome and its history survive intact.</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>FR-52 / AC-QS-12</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
+      <c r="Q71" s="6" t="inlineStr"/>
+      <c r="R71" s="4" t="inlineStr"/>
+      <c r="S71" s="4" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr"/>
+      <c r="U71" s="5" t="inlineStr"/>
+      <c r="V71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>1A-68</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>A quote linked to a deal with two options.</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Unlink the quote.</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Both the quote and the deal remain valid independent records, the deal no longer counts the removed option, and an audit event is written.</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>FR-55 / AC-QS-13</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
+      <c r="N72" s="7" t="inlineStr"/>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr"/>
+      <c r="Q72" s="9" t="inlineStr"/>
+      <c r="R72" s="7" t="inlineStr"/>
+      <c r="S72" s="7" t="inlineStr"/>
+      <c r="T72" s="7" t="inlineStr"/>
+      <c r="U72" s="8" t="inlineStr"/>
+      <c r="V72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>1A-69</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>A quote linked to a deal that holds three options.</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Go quote to deal with View Deal, then back to the same quote from the deal.</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Both directions land on the correct record and the round trip returns to the quote it started from. Neither step reaches an unrelated pipeline or the retired standalone quote page.</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>FR-56 / AC-QS-14</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr"/>
+      <c r="Q73" s="6" t="inlineStr"/>
+      <c r="R73" s="4" t="inlineStr"/>
+      <c r="S73" s="4" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="5" t="inlineStr"/>
+      <c r="V73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>1A-70</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>A migrated quote whose owning company was never set.</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Open the Quotes list as a user in a different company.</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>The quote is flagged for migration rather than shown. It never appears as belonging to the signed-in user's company.</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>FR-47 / AC-QS-07</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="7" t="inlineStr"/>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr"/>
+      <c r="Q74" s="9" t="inlineStr"/>
+      <c r="R74" s="7" t="inlineStr"/>
+      <c r="S74" s="7" t="inlineStr"/>
+      <c r="T74" s="7" t="inlineStr"/>
+      <c r="U74" s="8" t="inlineStr"/>
+      <c r="V74" s="9" t="inlineStr"/>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>1A-71</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>A deal with three options; one has just been accepted.</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Replay the acceptance event.</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>The replay is recognised as already handled. No second invoice, activity entry or stage transition is produced, and the sibling outcomes are unchanged.</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>FR-17 / AC-DEAL-07</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr"/>
+      <c r="Q75" s="6" t="inlineStr"/>
+      <c r="R75" s="4" t="inlineStr"/>
+      <c r="S75" s="4" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr"/>
+      <c r="U75" s="5" t="inlineStr"/>
+      <c r="V75" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:V58"/>
-  <conditionalFormatting sqref="K5:K58">
+  <autoFilter ref="A4:V75"/>
+  <conditionalFormatting sqref="K5:K75">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14247,13 +17401,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="K5:K58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K5:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E5:E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Manual,Automated,Both"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14273,9 +17427,9 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
@@ -14921,7 +18075,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Idempotency</t>
+          <t>Retry creates nothing twice</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -17089,12 +20243,12 @@
       <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Cells outstanding</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <f>COUNTIF(E5:M16,"Fail")+COUNTIF(E5:M16,"Blocked")+COUNTIF(E5:M16,"Not run")</f>
         <v/>
       </c>

--- a/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
+++ b/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivery gate'!$A$4:$J$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Traceability'!$A$4:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Use Case Coverage'!$A$4:$Y$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase 1A'!$A$4:$V$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase 1A'!$A$4:$V$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase 1B'!$A$4:$V$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Recipe coverage'!$A$4:$N$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase 1C'!$A$4:$V$43</definedName>
@@ -7035,31 +7035,31 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA('Phase 1A'!$A$5:$A$75)</f>
+        <f>COUNTA('Phase 1A'!$A$5:$A$76)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Fail")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$76,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Blocked")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$76,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"N/A")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$76,"N/A")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>COUNTIF('Phase 1A'!$K$5:$K$75,"Not run")</f>
+        <f>COUNTIF('Phase 1A'!$K$5:$K$76,"Not run")</f>
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>COUNTIFS('Phase 1A'!$E$5:$E$75,"P1")-COUNTIFS('Phase 1A'!$E$5:$E$75,"P1",'Phase 1A'!$K$5:$K$75,"Pass")-COUNTIFS('Phase 1A'!$E$5:$E$75,"P1",'Phase 1A'!$K$5:$K$75,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")+COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
+        <f>COUNTIFS('Phase 1A'!$E$5:$E$76,"P1")-COUNTIFS('Phase 1A'!$E$5:$E$76,"P1",'Phase 1A'!$K$5:$K$76,"Pass")-COUNTIFS('Phase 1A'!$E$5:$E$76,"P1",'Phase 1A'!$K$5:$K$76,"N/A")+COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"Pass")-COUNTIFS(Regression!$C$5:$C$10,"Phase 1A",Regression!$E$5:$E$10,"P1",Regression!$K$5:$K$10,"N/A")+COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"Pass")-COUNTIFS('Non-functional'!$C$5:$C$20,"Phase 1A",'Non-functional'!$E$5:$E$20,"P1",'Non-functional'!$K$5:$K$20,"N/A")+COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"Pass")-COUNTIFS('Use Case Coverage'!$C$5:$C$24,"Phase 1A",'Use Case Coverage'!$E$5:$E$24,"P1",'Use Case Coverage'!$K$5:$K$24,"N/A")</f>
         <v/>
       </c>
       <c r="I5" s="11">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>(COUNTIFS('Phase 1A'!$K$5:$K$75,"N/A")-COUNTIFS('Phase 1A'!$K$5:$K$75,"N/A",'Phase 1A'!$S$5:$S$75,"&lt;&gt;",'Phase 1A'!$V$5:$V$75,"&lt;&gt;"))+(COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A")-COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A",'Phase 1B'!$S$5:$S$29,"&lt;&gt;",'Phase 1B'!$V$5:$V$29,"&lt;&gt;"))+(COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A")-COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A",'Phase 1C'!$S$5:$S$43,"&lt;&gt;",'Phase 1C'!$V$5:$V$43,"&lt;&gt;"))+(COUNTIFS('Regression'!$K$5:$K$10,"N/A")-COUNTIFS('Regression'!$K$5:$K$10,"N/A",'Regression'!$S$5:$S$10,"&lt;&gt;",'Regression'!$V$5:$V$10,"&lt;&gt;"))+(COUNTIFS('Non-functional'!$K$5:$K$20,"N/A")-COUNTIFS('Non-functional'!$K$5:$K$20,"N/A",'Non-functional'!$S$5:$S$20,"&lt;&gt;",'Non-functional'!$V$5:$V$20,"&lt;&gt;"))+(COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A")-COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A",'Use Case Coverage'!$S$5:$S$24,"&lt;&gt;",'Use Case Coverage'!$V$5:$V$24,"&lt;&gt;"))</f>
+        <f>(COUNTIFS('Phase 1A'!$K$5:$K$76,"N/A")-COUNTIFS('Phase 1A'!$K$5:$K$76,"N/A",'Phase 1A'!$S$5:$S$76,"&lt;&gt;",'Phase 1A'!$V$5:$V$76,"&lt;&gt;"))+(COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A")-COUNTIFS('Phase 1B'!$K$5:$K$29,"N/A",'Phase 1B'!$S$5:$S$29,"&lt;&gt;",'Phase 1B'!$V$5:$V$29,"&lt;&gt;"))+(COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A")-COUNTIFS('Phase 1C'!$K$5:$K$43,"N/A",'Phase 1C'!$S$5:$S$43,"&lt;&gt;",'Phase 1C'!$V$5:$V$43,"&lt;&gt;"))+(COUNTIFS('Regression'!$K$5:$K$10,"N/A")-COUNTIFS('Regression'!$K$5:$K$10,"N/A",'Regression'!$S$5:$S$10,"&lt;&gt;",'Regression'!$V$5:$V$10,"&lt;&gt;"))+(COUNTIFS('Non-functional'!$K$5:$K$20,"N/A")-COUNTIFS('Non-functional'!$K$5:$K$20,"N/A",'Non-functional'!$S$5:$S$20,"&lt;&gt;",'Non-functional'!$V$5:$V$20,"&lt;&gt;"))+(COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A")-COUNTIFS('Use Case Coverage'!$K$5:$K$24,"N/A",'Use Case Coverage'!$S$5:$S$24,"&lt;&gt;",'Use Case Coverage'!$V$5:$V$24,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="B20" s="19">
-        <f>COUNTA('Phase 1A'!$A$5:$A$75)+COUNTA('Phase 1B'!$A$5:$A$29)+COUNTA('Phase 1C'!$A$5:$A$43)</f>
+        <f>COUNTA('Phase 1A'!$A$5:$A$76)+COUNTA('Phase 1B'!$A$5:$A$29)+COUNTA('Phase 1C'!$A$5:$A$43)</f>
         <v/>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-08",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-08",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J5" s="25" t="inlineStr">
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-14",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-14",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -9904,7 +9904,7 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-15",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-15",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J8" s="6" t="inlineStr"/>
@@ -9927,7 +9927,7 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-16",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-16",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-17",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-17",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="I12" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-19",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-19",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J12" s="25" t="inlineStr">
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="I21" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-63",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-63",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J21" s="9" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-58",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-58",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J22" s="6" t="inlineStr"/>
@@ -10389,7 +10389,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-60",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-60",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="I24" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-61",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-61",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J24" s="9" t="inlineStr"/>
@@ -10457,7 +10457,7 @@
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="8" t="inlineStr"/>
       <c r="I25" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-66",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-66",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J25" s="9" t="inlineStr"/>
@@ -10480,7 +10480,7 @@
       <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr"/>
       <c r="I26" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-67",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-67",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
@@ -10503,7 +10503,7 @@
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
       <c r="I27" s="8">
-        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$75,MATCH("1A-68",'Phase 1A'!$A$5:$A$75,0)),"not found")</f>
+        <f>IFERROR(INDEX('Phase 1A'!$K$5:$K$76,MATCH("1A-68",'Phase 1A'!$A$5:$A$76,0)),"not found")</f>
         <v/>
       </c>
       <c r="J27" s="9" t="inlineStr"/>
@@ -10815,7 +10815,7 @@
         <v>3</v>
       </c>
       <c r="X5" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-01",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-02",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-08",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-01",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-02",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-08",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y5" s="6">
@@ -10894,7 +10894,7 @@
         <v>3</v>
       </c>
       <c r="X6" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-09",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-10",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-11",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-09",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-10",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-11",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y6" s="9">
@@ -10973,7 +10973,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-12",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-12",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y7" s="6">
@@ -11052,7 +11052,7 @@
         <v>2</v>
       </c>
       <c r="X8" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-13",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-09",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-13",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-09",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y8" s="9">
@@ -11131,7 +11131,7 @@
         <v>3</v>
       </c>
       <c r="X9" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-31",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-30",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-32",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-31",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-30",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-32",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y9" s="6">
@@ -11210,7 +11210,7 @@
         <v>3</v>
       </c>
       <c r="X10" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-16",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-14",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-45",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-16",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-14",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-45",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y10" s="9">
@@ -11289,7 +11289,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-19",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-19",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y11" s="6">
@@ -11368,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="X12" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-18",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-18",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y12" s="9">
@@ -11447,7 +11447,7 @@
         <v>3</v>
       </c>
       <c r="X13" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-34",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-35",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-37",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-34",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-35",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-37",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y13" s="6">
@@ -11526,7 +11526,7 @@
         <v>3</v>
       </c>
       <c r="X14" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-38",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-40",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-42",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-38",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-40",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-42",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y14" s="9">
@@ -11605,7 +11605,7 @@
         <v>2</v>
       </c>
       <c r="X15" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-47",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-04",'Phase 1B'!$K$5:$K$29,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-47",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1B'!$A$5:$A$29,"1B-04",'Phase 1B'!$K$5:$K$29,"Pass")</f>
         <v/>
       </c>
       <c r="Y15" s="6">
@@ -12237,7 +12237,7 @@
         <v>4</v>
       </c>
       <c r="X23" s="5">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-58",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-59",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-60",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-69",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-58",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-59",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-60",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-69",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y23" s="6">
@@ -12316,7 +12316,7 @@
         <v>4</v>
       </c>
       <c r="X24" s="8">
-        <f>COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-61",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-64",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-66",'Phase 1A'!$K$5:$K$75,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$75,"1A-68",'Phase 1A'!$K$5:$K$75,"Pass")</f>
+        <f>COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-61",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-64",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-66",'Phase 1A'!$K$5:$K$76,"Pass")+COUNTIFS('Phase 1A'!$A$5:$A$76,"1A-68",'Phase 1A'!$K$5:$K$76,"Pass")</f>
         <v/>
       </c>
       <c r="Y24" s="9">
@@ -12393,7 +12393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17381,9 +17381,77 @@
       <c r="U75" s="5" t="inlineStr"/>
       <c r="V75" s="6" t="inlineStr"/>
     </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>1A-72</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1A</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Quote &amp; Sales</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>A quote workspace open on one option, with a sibling option on the same deal.</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Switch to the sibling option, open a different workspace section, then copy the address and open it in a fresh session.</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>The address follows the record and the section the whole way. The copied link opens the option and section that were on screen, not whichever quote the workspace was first opened with, and a refresh does the same.</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>FR-57 / AC-QS-15</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr"/>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr"/>
+      <c r="Q76" s="9" t="inlineStr"/>
+      <c r="R76" s="7" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr"/>
+      <c r="T76" s="7" t="inlineStr"/>
+      <c r="U76" s="8" t="inlineStr"/>
+      <c r="V76" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:V75"/>
-  <conditionalFormatting sqref="K5:K75">
+  <autoFilter ref="A4:V76"/>
+  <conditionalFormatting sqref="K5:K76">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -17401,13 +17469,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="K5:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K5:K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E5:E76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Manual,Automated,Both"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
+++ b/docs/WeQuote-CRM-Phase-1-QA-Checklist.xlsx
@@ -1125,12 +1125,12 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Open Create Automation.</t>
+          <t>Open Create Automation for a fixed stage.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Exactly two routes: start from a recipe, or start from scratch.</t>
+          <t>Exactly one route: the twelve templates for that stage. No 'start from scratch' entry, no empty canvas, and no way to reach one by URL or keyboard.</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
